--- a/ics_topologies/chemical_processing_plant/chemical_processing_plant.xlsx
+++ b/ics_topologies/chemical_processing_plant/chemical_processing_plant.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R33"/>
+  <dimension ref="A1:S61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,65 +445,70 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>purdue_level</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>description</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>criticality</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>vendor</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ip</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>cvss_type</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>exposed</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>patched</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>consequence_severity</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>role</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>awareness</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>privilege</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>p_base_override</t>
         </is>
@@ -517,7 +522,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Corporate Firewall</t>
+          <t>Internet Edge Firewall</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -537,59 +542,64 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Internet edge</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>Corporate internet edge firewall</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Palo Alto</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>PA-5250</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
         <is>
           <t>7.5</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>9.0</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CHEM-ENT-SW-001</t>
+          <t>CHEM-ENT-WS-001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Enterprise Switch</t>
+          <t>Business Workstation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -599,7 +609,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Network Switch</t>
+          <t>Workstation</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -609,59 +619,64 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Corporate network</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Corporate user workstation on the business LAN</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Catalyst 9300</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
+          <t>Dell</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>OptiPlex 7000</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CHEM-ENT-DC-001</t>
+          <t>CHEM-ENT-SW-001</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Domain Controller</t>
+          <t>Enterprise Core Switch</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -671,7 +686,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Server</t>
+          <t>Network Switch</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -681,59 +696,64 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AD</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>Core corporate network switch</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Windows Server 2022</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>8.1</t>
-        </is>
-      </c>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Catalyst 9300</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CHEM-ENT-ERP-001</t>
+          <t>CHEM-ENT-DC-001</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ERP Server</t>
+          <t>Domain Controller</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -753,59 +773,64 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ERP</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Active Directory for the corporate domain</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>S/4HANA</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Windows Server 2022</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CHEM-DMZ-SW-001</t>
+          <t>CHEM-ENT-ERP-001</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DMZ Switch</t>
+          <t>ERP Server</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -815,69 +840,74 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Network Switch</t>
+          <t>Server</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>DMZ</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Process DMZ</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Enterprise resource planning (SAP S/4HANA)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>IE 4000</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>S/4HANA</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CHEM-DMZ-HIST-001</t>
+          <t>CHEM-ENT-FW-002</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Historian</t>
+          <t>Enterprise Firewall</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -887,69 +917,74 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Server</t>
+          <t>Firewall</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>DMZ</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Plant historian</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>Enterprise-to-IDMZ boundary firewall (stateful, allow-list)</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>OSIsoft</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PI Server</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
+          <t>Palo Alto</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>PA-3260</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CHEM-DMZ-JUMP-001</t>
+          <t>CHEM-IDMZ-SW-001</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jump Server</t>
+          <t>IDMZ Switch</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -959,69 +994,74 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Server</t>
+          <t>Network Switch</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>DMZ</t>
+          <t>IDMZ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>OT jump host</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>Industrial DMZ network switch</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Windows Server 2022</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>8.1</t>
-        </is>
-      </c>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>IE 4000</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CHEM-DCS-SW-001</t>
+          <t>CHEM-IDMZ-JUMP-001</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DCS Switch</t>
+          <t>Jump Server</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1031,69 +1071,74 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Network Switch</t>
+          <t>Server</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>DCS</t>
+          <t>IDMZ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>DCS backbone</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>Bastion host for controlled administrative access into OT</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Siemens</t>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SCALANCE XM408</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Windows Server 2022</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CHEM-DCS-OP-001</t>
+          <t>CHEM-IDMZ-DB-001</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Operator Station</t>
+          <t>Data Broker</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1103,69 +1148,74 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Workstation</t>
+          <t>Gateway</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>DCS</t>
+          <t>IDMZ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>DCS operator console</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>OPC UA data broker bridging OT data to the enterprise (unidirectional publisher)</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Siemens</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SIMATIC PCS 7</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
+          <t>Software Toolbox</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Cogent DataHub</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CHEM-DCS-ENG-001</t>
+          <t>CHEM-IDMZ-HIST-001</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Engineering Station</t>
+          <t>Historian Replica</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1175,69 +1225,74 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Workstation</t>
+          <t>Server</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>DCS</t>
+          <t>IDMZ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>DCS engineering</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Read-only historian replica serving the enterprise</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SIMATIC PCS 7</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>7.8</t>
-        </is>
-      </c>
+          <t>OSIsoft</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>PI Server</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr"/>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CHEM-DCS-CTRL-001</t>
+          <t>CHEM-IDMZ-RAG-001</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DCS Controller (Reactor)</t>
+          <t>Remote Access Gateway</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1247,69 +1302,74 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>DCSController</t>
+          <t>Gateway</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>DCS</t>
+          <t>IDMZ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Reactor temperature/pressure control</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>VPN concentrator terminating vendor/support remote sessions</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Siemens</t>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AS 410</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
+          <t>Palo Alto</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>GlobalProtect</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr"/>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CHEM-DCS-CTRL-002</t>
+          <t>CHEM-IDMZ-PATCH-001</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DCS Controller (Distillation)</t>
+          <t>Patch &amp; Update Repository</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1319,69 +1379,74 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>DCSController</t>
+          <t>Server</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>DCS</t>
+          <t>IDMZ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Distillation column control</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Staged patch/AV signature repository for OT hosts</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AS 410</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>WSUS</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr"/>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CHEM-DCS-CTRL-003</t>
+          <t>CHEM-IDMZ-FW-001</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DCS Controller (Utilities)</t>
+          <t>OT Firewall</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1391,69 +1456,74 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>DCSController</t>
+          <t>Firewall</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>DCS</t>
+          <t>IDMZ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Utilities (steam, cooling)</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>OT-side firewall between the IDMZ and the site operations network</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AS 410</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
+          <t>Palo Alto</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>PA-3260</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CHEM-SIS-PLC-001</t>
+          <t>CHEM-OPS-SW-001</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Safety PLC</t>
+          <t>Operations Switch</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1463,837 +1533,998 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SafetyPLC</t>
+          <t>Network Switch</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SIS</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Safety Instrumented System</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
+          <t>Site operations (L3) network switch</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>Siemens</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>S7-400F</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>SCALANCE XM408</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CHEM-SIS-ESD-001</t>
+          <t>CHEM-OPS-OP-001</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ESD Switch</t>
+          <t>Operator Station 1 (HMI)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>physical</t>
+          <t>device</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SafetyDevice</t>
+          <t>Workstation</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SIS</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Emergency shutdown button</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t>Primary DCS operator console in the control room</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Pilz</t>
-        </is>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>PNOZ</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>SIMATIC PCS 7</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr"/>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CHEM-SIS-RELAY-001</t>
+          <t>CHEM-OPS-OP-002</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ESD Relay</t>
+          <t>Operator Station 2 (HMI)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>physical</t>
+          <t>device</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SafetyRelay</t>
+          <t>Workstation</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SIS</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Safety relay</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
+          <t>Backup DCS operator console (utilities area)</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Pilz</t>
-        </is>
-      </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>PNOZ X3</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>SIMATIC PCS 7</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr"/>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CHEM-FLD-TC-001</t>
+          <t>CHEM-OPS-ENG-001</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Thermocouple (Reactor)</t>
+          <t>Engineering Workstation</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>physical</t>
+          <t>device</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Workstation</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Field</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Reactor temperature</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
+          <t>DCS engineering station (configuration, logic, recipes)</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Emerson</t>
-        </is>
-      </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Rosemount 214</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>SIMATIC PCS 7 ES</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CHEM-FLD-PT-001</t>
+          <t>CHEM-OPS-HIST-001</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pressure Transmitter (Reactor)</t>
+          <t>OT Historian</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>physical</t>
+          <t>device</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Server</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Field</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Reactor pressure</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
+          <t>Primary plant historian collecting process data</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Emerson</t>
-        </is>
-      </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Rosemount 3051</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
+          <t>OSIsoft</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>PI Server</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr"/>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CHEM-FLD-LT-001</t>
+          <t>CHEM-OPS-APP-001</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Level Transmitter (Reactor)</t>
+          <t>DCS Application Server</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>physical</t>
+          <t>device</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Server</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Field</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Reactor level</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
+          <t>PCS 7 application/OPC UA server serving the operator clients</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Emerson</t>
-        </is>
-      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Rosemount 3300</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>SIMATIC PCS 7 AS</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr"/>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CHEM-FLD-CV-001</t>
+          <t>CHEM-CTL-SW-001</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Control Valve (Reactor)</t>
+          <t>Control Switch</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>physical</t>
+          <t>device</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Valve</t>
+          <t>Network Switch</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Field</t>
+          <t>Control</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Feed control valve</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
+          <t>Redundant L2 control network switch fabric</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Emerson</t>
-        </is>
-      </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Fisher V500</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>SCALANCE XM408</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CHEM-FLD-TC-002</t>
+          <t>CHEM-CTL-DCS-001</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Thermocouple (Distillation)</t>
+          <t>DCS Controller — Reactor Area</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>physical</t>
+          <t>device</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>DCSController</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Field</t>
+          <t>Control</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Column temperature</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
+          <t>Reactor temperature/pressure/level control loop processor</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Emerson</t>
-        </is>
-      </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Rosemount 214</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>SIMATIC PCS 7 AS 410</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr"/>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CHEM-FLD-PT-002</t>
+          <t>CHEM-CTL-DCS-002</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pressure Transmitter (Distillation)</t>
+          <t>DCS Controller — Distillation Area</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>physical</t>
+          <t>device</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>DCSController</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Field</t>
+          <t>Control</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Column pressure</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
+          <t>Distillation column control loop processor</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Emerson</t>
-        </is>
-      </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Rosemount 3051</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>SIMATIC PCS 7 AS 410</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr"/>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CHEM-FLD-FT-001</t>
+          <t>CHEM-CTL-DCS-003</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Flow Transmitter (Distillation)</t>
+          <t>DCS Controller — Utilities &amp; Offsites</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>physical</t>
+          <t>device</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>DCSController</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Field</t>
+          <t>Control</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Reflux flow</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Utilities, storage and tank-farm control loop processor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Emerson</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Rosemount 8700</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>SIMATIC PCS 7 AS 410</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr"/>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CHEM-FLD-CV-002</t>
+          <t>CHEM-SIS-GW-001</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Control Valve (Distillation)</t>
+          <t>SIS Status Gateway</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>physical</t>
+          <t>device</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Valve</t>
+          <t>Gateway</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Field</t>
+          <t>SIS</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Reflux valve</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
+          <t>Certified status-only interface between the DCS and the SIS</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Emerson</t>
-        </is>
-      </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Fisher V500</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
+          <t>HIMA</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>HIQuad X Gateway</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr"/>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CHEM-FLD-PUMP-001</t>
+          <t>CHEM-SIS-LS-001</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Product Pump</t>
+          <t>Safety Logic Solver</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>physical</t>
+          <t>device</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Pump</t>
+          <t>SafetyPLC</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Field</t>
+          <t>SIS</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Transfer pump to storage</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
+          <t>SIL-3 certified safety logic solver executing ESD logic</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Grundfos</t>
-        </is>
-      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>CR 64</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
+          <t>HIMA</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>HIQuad X</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr"/>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CHEM-FLD-VALVE-001</t>
+          <t>CHEM-SIS-ENG-001</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Storage Tank Valve</t>
+          <t>SIS Engineering Workstation</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>physical</t>
+          <t>device</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Valve</t>
+          <t>Workstation</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Field</t>
+          <t>SIS</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tank inlet/outlet</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Dedicated engineering station for SIS logic (isolated from the DCS engineering LAN)</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Emerson</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Fisher V500</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
+          <t>HIMA</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>SIMATIC Manager SIS</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr"/>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CHEM-FLD-SENSOR-001</t>
+          <t>CHEM-SIS-PT-001</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tank Level Sensor</t>
+          <t>High-Integrity Pressure Transmitter</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2303,47 +2534,52 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Transmitter</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Field</t>
+          <t>SIS</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Storage tank level</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>SIL-rated pressure transmitter on the reactor (SIS input)</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
           <t>Emerson</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Rosemount 3300</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Rosemount 3051S</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr">
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
@@ -2352,156 +2588,150 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CHEM-REM-SW-001</t>
+          <t>CHEM-SIS-TT-001</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Remote Switch</t>
+          <t>High-Integrity Temperature Transmitter</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>physical</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Network Switch</t>
+          <t>Transmitter</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>SIS</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Switch at remote tank farm</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>SIL-rated temperature element on the reactor (SIS input)</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>SCALANCE XB208</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr"/>
+          <t>Emerson</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Rosemount 214S</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CHEM-REM-RTU-001</t>
+          <t>CHEM-SIS-SOV-001</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Remote RTU</t>
+          <t>Safety Shutoff Valve (Feed)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>physical</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>RTU</t>
+          <t>SafetyValve</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>SIS</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>RTU for tank farm</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
+          <t>Fail-closed SIS final element isolating the reactor feed</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Control Microsystems</t>
-        </is>
-      </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>SCADAPack 470</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr"/>
+          <t>Emerson</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Fisher FIELDVUE DVC6200</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CHEM-REM-PUMP-001</t>
+          <t>CHEM-SIS-SOV-002</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Remote Transfer Pump</t>
+          <t>Emergency Depressurization Valve</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2511,179 +2741,2158 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Pump</t>
+          <t>SafetyValve</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>SIS</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pump to rail cars</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
+          <t>Fail-open SIS final element venting the reactor to the flare (safe state)</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Grundfos</t>
-        </is>
-      </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>CR 90</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
+          <t>Emerson</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Fisher FIELDVUE DVC6200</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>0.02</t>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>0.01</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CHEM-REM-VALVE-001</t>
+          <t>CHEM-FLD-IO-001</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Remote Valve</t>
+          <t>Field Remote I/O Rack</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>physical</t>
+          <t>device</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Valve</t>
+          <t>RemoteIO</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Field</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rail loading valve</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Fieldbus remote I/O marshalling rack feeding the DCS controllers</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Emerson</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Fisher V500</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>ET 200M</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr"/>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CHEM-HUM-OPR-001</t>
+          <t>CHEM-FLD-TT-001</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Process Operator</t>
+          <t>Temperature Transmitter (Reactor)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>physical</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Operator</t>
+          <t>Transmitter</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>DCS</t>
+          <t>Field</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Board operator supervising the DCS</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>Reactor temperature (thermocouple) transmitter</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Emerson</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Rosemount 214</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr">
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>CHEM-FLD-PT-001</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Pressure Transmitter (Reactor)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Transmitter</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Reactor pressure transmitter</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Emerson</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Rosemount 3051</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>CHEM-FLD-LT-001</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Level Transmitter (Reactor)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Transmitter</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Reactor level transmitter</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Emerson</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Rosemount 3300</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>CHEM-FLD-FCV-001</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Feed Control Valve (Reactor)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ControlValve</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Reactor feed flow control valve (final element)</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Emerson</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Fisher V500</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>CHEM-FLD-PUMP-001</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Reactor Feed Pump</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Pump</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Centrifugal feed pump supplying the reactor</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Grundfos</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>CR 64</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>CHEM-FLD-VFD-001</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Feed Pump VFD</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>device</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VFD</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Variable frequency drive for the reactor feed pump</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>ACS880</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>CHEM-FLD-TT-002</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Temperature Transmitter (Column)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Transmitter</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Distillation column temperature transmitter</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Emerson</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Rosemount 214</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>CHEM-FLD-PT-002</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Pressure Transmitter (Column)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Transmitter</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Distillation column pressure transmitter</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Emerson</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Rosemount 3051</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>CHEM-FLD-FT-001</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Flow Transmitter (Reflux)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Transmitter</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Column reflux flow transmitter</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Emerson</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Rosemount 8700</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>CHEM-FLD-FCV-002</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Reflux Control Valve</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ControlValve</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Column reflux control valve (final element)</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Emerson</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Fisher V500</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>CHEM-FLD-FCV-003</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Steam Reboiler Control Valve</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ControlValve</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Reboiler steam supply control valve (final element)</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Emerson</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Fisher V500</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>CHEM-FLD-LT-002</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Level Transmitter (Storage)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Transmitter</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Product storage tank level transmitter</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Emerson</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Rosemount 3300</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>CHEM-FLD-SENSOR-001</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Cooling Water Flow Transmitter</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Transmitter</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Cooling water flow transmitter</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Emerson</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Rosemount 8700</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>CHEM-FLD-VALVE-001</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Cooling Water Control Valve</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>ControlValve</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Cooling water supply control valve</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Emerson</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Fisher V500</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>CHEM-FLD-PUMP-002</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Product Transfer Pump</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Pump</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Product transfer pump to storage</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Grundfos</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>CR 90</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>CHEM-PRO-REACTOR-001</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Reactor Vessel</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Reactor</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Exothermic stirred-tank reactor — primary hazard source</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Zeton</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>CSTR-10m3</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>CHEM-PRO-COLUMN-001</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Distillation Column</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>DistillationColumn</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Continuous distillation column separating the reactor product</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Sulzer</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Packed Column</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>CHEM-PRO-HX-001</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Heat Exchanger (Reboiler)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>HeatExchanger</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Steam reboiler providing column heat input</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Alfa Laval</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>CHEM-PRO-PIPE-001</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Reactor-to-Column Transfer Piping</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Product transfer line from the reactor to the distillation column</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>DN150</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>0.005</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>CHEM-PRO-TANK-001</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Product Storage Tank</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>StorageTank</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Finished product storage tank</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Chicago Bridge &amp; Iron</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Fixed Roof 500m3</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>CHEM-PRO-TANK-002</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Feedstock Storage Tank</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>StorageTank</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Raw feedstock storage tank feeding the reactor</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Chicago Bridge &amp; Iron</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Fixed Roof 1000m3</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>CHEM-REM-SW-001</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Remote Site Switch</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>device</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Network Switch</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Industrial switch at the remote tank farm</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>SCALANCE XB208</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>CHEM-REM-RTU-001</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Remote RTU — Tank Farm</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>device</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>RTU</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Remote terminal unit controlling tank-farm loading</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Control Microsystems</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>SCADAPack 470</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>CHEM-REM-LT-001</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Remote Tank Level Transmitter</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Transmitter</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Level transmitter on the remote product tank</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Emerson</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Rosemount 3300</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>CHEM-REM-PUMP-001</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Remote Transfer Pump</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Pump</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Transfer pump at the remote tank farm</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Grundfos</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>CR 90</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>CHEM-REM-VALVE-001</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Rail Loading Valve</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>ControlValve</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Rail-car loading isolation valve at the tank farm</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Emerson</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Fisher V500</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>CHEM-REM-TANK-001</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Remote Product Tank</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>StorageTank</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Product storage tank at the remote tank farm</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Chicago Bridge &amp; Iron</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Floating Roof 2000m3</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>CHEM-HUM-OPR-001</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Process Operator</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Operator</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Board operator supervising the DCS from the control room</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="P60" t="inlineStr">
         <is>
           <t>operator</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="Q60" t="inlineStr">
         <is>
           <t>0.4</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="R60" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>CHEM-HUM-ENG-001</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Control Systems Engineer</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Engineer maintaining DCS configuration and control logic</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>engineer</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>elevated</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2696,7 +4905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:H82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2730,6 +4939,16 @@
           <t>trust</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>firewalled</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>transport</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2749,7 +4968,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>HTTPS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -2762,18 +4981,24 @@
           <t>low</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>CHEM-ENT-WS-001</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>CHEM-ENT-SW-001</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>CHEM-ENT-DC-001</t>
-        </is>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>connects-to</t>
@@ -2781,7 +5006,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LDAP</t>
+          <t>HTTPS</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2794,6 +5019,8 @@
           <t>high</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2803,7 +5030,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CHEM-ENT-ERP-001</t>
+          <t>CHEM-ENT-DC-001</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2813,7 +5040,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>LDAP</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2826,6 +5053,8 @@
           <t>high</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2835,7 +5064,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CHEM-DMZ-SW-001</t>
+          <t>CHEM-ENT-ERP-001</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2845,7 +5074,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>HTTPS</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2855,19 +5084,21 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CHEM-DMZ-SW-001</t>
+          <t>CHEM-ENT-SW-001</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CHEM-DMZ-HIST-001</t>
+          <t>CHEM-ENT-FW-002</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2877,7 +5108,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>OPC UA</t>
+          <t>HTTPS</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2890,16 +5121,22 @@
           <t>medium</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CHEM-DMZ-SW-001</t>
+          <t>CHEM-ENT-FW-002</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CHEM-DMZ-JUMP-001</t>
+          <t>CHEM-IDMZ-SW-001</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2909,7 +5146,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SSH</t>
+          <t>HTTPS</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2922,16 +5159,22 @@
           <t>medium</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CHEM-DMZ-JUMP-001</t>
+          <t>CHEM-IDMZ-SW-001</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CHEM-DCS-SW-001</t>
+          <t>CHEM-IDMZ-JUMP-001</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2941,7 +5184,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>RDP</t>
+          <t>SSH</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2954,16 +5197,18 @@
           <t>medium</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CHEM-DCS-SW-001</t>
+          <t>CHEM-IDMZ-SW-001</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CHEM-DCS-OP-001</t>
+          <t>CHEM-IDMZ-DB-001</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2983,19 +5228,21 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CHEM-DCS-SW-001</t>
+          <t>CHEM-IDMZ-SW-001</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CHEM-DCS-ENG-001</t>
+          <t>CHEM-IDMZ-HIST-001</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3015,19 +5262,21 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CHEM-DCS-SW-001</t>
+          <t>CHEM-IDMZ-SW-001</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CHEM-DCS-CTRL-001</t>
+          <t>CHEM-IDMZ-RAG-001</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3037,7 +5286,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>PROFIBUS</t>
+          <t>VPN</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -3047,19 +5296,21 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CHEM-DCS-SW-001</t>
+          <t>CHEM-IDMZ-SW-001</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CHEM-DCS-CTRL-002</t>
+          <t>CHEM-IDMZ-PATCH-001</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -3069,7 +5320,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>PROFIBUS</t>
+          <t>HTTPS</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -3079,19 +5330,21 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CHEM-DCS-SW-001</t>
+          <t>CHEM-IDMZ-RAG-001</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CHEM-DCS-CTRL-003</t>
+          <t>CHEM-IDMZ-JUMP-001</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -3101,7 +5354,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>PROFIBUS</t>
+          <t>RDP</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -3111,29 +5364,31 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CHEM-HUM-OPR-001</t>
+          <t>CHEM-IDMZ-SW-001</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CHEM-DCS-OP-001</t>
+          <t>CHEM-IDMZ-FW-001</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>programs / operates</t>
+          <t>connects-to</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>HMI</t>
+          <t>HTTPS</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -3143,29 +5398,35 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CHEM-DCS-CTRL-001</t>
+          <t>CHEM-IDMZ-FW-001</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CHEM-FLD-TC-001</t>
+          <t>CHEM-OPS-SW-001</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>monitors</t>
+          <t>connects-to</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>HART</t>
+          <t>OPC UA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -3175,29 +5436,35 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CHEM-DCS-CTRL-001</t>
+          <t>CHEM-IDMZ-JUMP-001</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CHEM-FLD-PT-001</t>
+          <t>CHEM-OPS-ENG-001</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>monitors</t>
+          <t>connects-to</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>HART</t>
+          <t>RDP</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3210,26 +5477,32 @@
           <t>low</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CHEM-DCS-CTRL-001</t>
+          <t>CHEM-OPS-SW-001</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CHEM-FLD-LT-001</t>
+          <t>CHEM-OPS-OP-001</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>monitors</t>
+          <t>connects-to</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HART</t>
+          <t>OPC UA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3239,61 +5512,65 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CHEM-DCS-CTRL-001</t>
+          <t>CHEM-OPS-SW-001</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CHEM-FLD-CV-001</t>
+          <t>CHEM-OPS-OP-002</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>actuates</t>
+          <t>connects-to</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>HART</t>
+          <t>OPC UA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>unidirectional</t>
+          <t>bidirectional</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CHEM-DCS-CTRL-002</t>
+          <t>CHEM-OPS-SW-001</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CHEM-FLD-TC-002</t>
+          <t>CHEM-OPS-ENG-001</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>monitors</t>
+          <t>connects-to</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HART</t>
+          <t>HTTPS</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3303,29 +5580,31 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CHEM-DCS-CTRL-002</t>
+          <t>CHEM-OPS-SW-001</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CHEM-FLD-PT-002</t>
+          <t>CHEM-OPS-HIST-001</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>monitors</t>
+          <t>connects-to</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>HART</t>
+          <t>OPC UA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -3335,29 +5614,31 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CHEM-DCS-CTRL-002</t>
+          <t>CHEM-OPS-SW-001</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CHEM-FLD-FT-001</t>
+          <t>CHEM-OPS-APP-001</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>monitors</t>
+          <t>connects-to</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>HART</t>
+          <t>OPC UA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -3367,61 +5648,65 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CHEM-DCS-CTRL-002</t>
+          <t>CHEM-HUM-OPR-001</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CHEM-FLD-CV-002</t>
+          <t>CHEM-OPS-OP-001</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>actuates</t>
+          <t>programs / operates</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>HART</t>
+          <t>HMI</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>unidirectional</t>
+          <t>bidirectional</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CHEM-DCS-CTRL-001</t>
+          <t>CHEM-HUM-OPR-001</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CHEM-SIS-PLC-001</t>
+          <t>CHEM-OPS-OP-002</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>connects-to</t>
+          <t>programs / operates</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>PROFIsafe</t>
+          <t>HMI</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3431,29 +5716,31 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CHEM-DCS-CTRL-002</t>
+          <t>CHEM-HUM-ENG-001</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CHEM-SIS-PLC-001</t>
+          <t>CHEM-OPS-ENG-001</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>connects-to</t>
+          <t>programs / operates</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>PROFIsafe</t>
+          <t>HTTPS</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3463,29 +5750,31 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CHEM-SIS-PLC-001</t>
+          <t>CHEM-OPS-SW-001</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CHEM-SIS-ESD-001</t>
+          <t>CHEM-CTL-SW-001</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>monitors</t>
+          <t>connects-to</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>PROFIsafe</t>
+          <t>PROFINET</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3495,29 +5784,35 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CHEM-SIS-PLC-001</t>
+          <t>CHEM-CTL-SW-001</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CHEM-SIS-RELAY-001</t>
+          <t>CHEM-CTL-DCS-001</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>monitors</t>
+          <t>connects-to</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>PROFIsafe</t>
+          <t>PROFINET</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3527,29 +5822,31 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CHEM-DCS-CTRL-003</t>
+          <t>CHEM-CTL-SW-001</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CHEM-REM-RTU-001</t>
+          <t>CHEM-CTL-DCS-002</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>controls</t>
+          <t>connects-to</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Modbus TCP</t>
+          <t>PROFINET</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3559,19 +5856,21 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CHEM-REM-RTU-001</t>
+          <t>CHEM-CTL-SW-001</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CHEM-REM-SW-001</t>
+          <t>CHEM-CTL-DCS-003</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3581,7 +5880,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Modbus TCP</t>
+          <t>PROFINET</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3591,169 +5890,1863 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CHEM-REM-RTU-001</t>
+          <t>CHEM-OPS-ENG-001</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CHEM-REM-PUMP-001</t>
+          <t>CHEM-CTL-DCS-001</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>actuates</t>
+          <t>programs / operates</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Modbus TCP</t>
+          <t>PROFINET</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>unidirectional</t>
+          <t>bidirectional</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CHEM-REM-RTU-001</t>
+          <t>CHEM-OPS-ENG-001</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CHEM-REM-VALVE-001</t>
+          <t>CHEM-CTL-DCS-002</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>actuates</t>
+          <t>programs / operates</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Modbus TCP</t>
+          <t>PROFINET</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>unidirectional</t>
+          <t>bidirectional</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CHEM-DCS-CTRL-003</t>
+          <t>CHEM-OPS-ENG-001</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CHEM-FLD-PUMP-001</t>
+          <t>CHEM-CTL-DCS-003</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>actuates</t>
+          <t>programs / operates</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Modbus TCP</t>
+          <t>PROFINET</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>unidirectional</t>
+          <t>bidirectional</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CHEM-DCS-CTRL-003</t>
+          <t>CHEM-OPS-OP-001</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CHEM-FLD-VALVE-001</t>
+          <t>CHEM-OPS-APP-001</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>actuates</t>
+          <t>connects-to</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Modbus TCP</t>
+          <t>OPC UA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>unidirectional</t>
+          <t>bidirectional</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CHEM-DCS-CTRL-003</t>
+          <t>CHEM-OPS-OP-002</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>CHEM-OPS-APP-001</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>connects-to</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>OPC UA</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>bidirectional</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>CHEM-OPS-APP-001</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>CHEM-CTL-DCS-001</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>connects-to</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>OPC UA</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>bidirectional</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>CHEM-OPS-APP-001</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>CHEM-CTL-DCS-002</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>connects-to</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>OPC UA</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>bidirectional</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>CHEM-OPS-APP-001</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>CHEM-CTL-DCS-003</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>connects-to</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>OPC UA</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>bidirectional</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>CHEM-OPS-HIST-001</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>CHEM-CTL-DCS-001</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>connects-to</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>OPC UA</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>bidirectional</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>CHEM-OPS-HIST-001</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>CHEM-CTL-DCS-002</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>connects-to</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>OPC UA</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>bidirectional</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>CHEM-FLD-TT-001</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>CHEM-CTL-DCS-001</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>monitors</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>HART</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>bidirectional</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>CHEM-FLD-PT-001</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>CHEM-CTL-DCS-001</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>monitors</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>HART</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>bidirectional</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>CHEM-FLD-LT-001</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>CHEM-CTL-DCS-001</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>monitors</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>HART</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>bidirectional</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>CHEM-FLD-IO-001</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>CHEM-CTL-DCS-001</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>connects-to</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>PROFIBUS</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>bidirectional</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>CHEM-FLD-IO-001</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>CHEM-CTL-DCS-002</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>connects-to</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>PROFIBUS</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>bidirectional</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>CHEM-CTL-DCS-001</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CHEM-FLD-FCV-001</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>actuates</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>HART</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>unidirectional</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>CHEM-CTL-DCS-001</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CHEM-FLD-PUMP-001</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>controls</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>PROFINET</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>unidirectional</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>CHEM-CTL-DCS-001</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>CHEM-FLD-VFD-001</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>actuates</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>PROFINET</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>bidirectional</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>CHEM-FLD-TT-002</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>CHEM-CTL-DCS-002</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>monitors</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>HART</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>bidirectional</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>CHEM-FLD-PT-002</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>CHEM-CTL-DCS-002</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>monitors</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>HART</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>bidirectional</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>CHEM-FLD-FT-001</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>CHEM-CTL-DCS-002</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>monitors</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>HART</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>bidirectional</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>CHEM-CTL-DCS-002</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>CHEM-FLD-FCV-002</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>actuates</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>HART</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>unidirectional</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>CHEM-CTL-DCS-002</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>CHEM-FLD-FCV-003</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>actuates</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>HART</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>unidirectional</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>CHEM-FLD-LT-002</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>CHEM-CTL-DCS-003</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>monitors</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Modbus TCP</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>bidirectional</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
           <t>CHEM-FLD-SENSOR-001</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CHEM-CTL-DCS-003</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
         <is>
           <t>monitors</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>Modbus TCP</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>bidirectional</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>CHEM-CTL-DCS-003</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>CHEM-FLD-VALVE-001</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>actuates</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Modbus TCP</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>unidirectional</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>CHEM-CTL-DCS-003</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>CHEM-FLD-PUMP-002</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>controls</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Modbus TCP</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>unidirectional</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>CHEM-CTL-DCS-001</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>CHEM-SIS-GW-001</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>connects-to</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>PROFIsafe</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>bidirectional</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>CHEM-SIS-GW-001</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>CHEM-SIS-LS-001</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>connects-to</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>PROFIsafe</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>bidirectional</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>CHEM-SIS-PT-001</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>CHEM-SIS-LS-001</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>monitors</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>PROFIsafe</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>bidirectional</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>CHEM-SIS-TT-001</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>CHEM-SIS-LS-001</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>monitors</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>PROFIsafe</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>bidirectional</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>CHEM-SIS-ENG-001</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>CHEM-SIS-LS-001</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>programs / operates</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>PROFIsafe</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>bidirectional</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>CHEM-SIS-LS-001</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>CHEM-SIS-SOV-001</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>actuates</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>PROFIsafe</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>unidirectional</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>CHEM-SIS-LS-001</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>CHEM-SIS-SOV-002</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>actuates</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>PROFIsafe</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>unidirectional</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>CHEM-FLD-FCV-001</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>CHEM-PRO-REACTOR-001</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>actuates</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>HART</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>unidirectional</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>CHEM-FLD-PUMP-001</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>CHEM-PRO-REACTOR-001</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>actuates</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>PROFINET</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>unidirectional</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>CHEM-FLD-PUMP-001</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>CHEM-PRO-PIPE-001</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>actuates</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>PROFINET</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>unidirectional</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>CHEM-FLD-PUMP-001</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>CHEM-PRO-TANK-002</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>actuates</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>PROFINET</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>unidirectional</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>CHEM-FLD-LT-002</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>CHEM-PRO-TANK-002</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>monitors</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Modbus TCP</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>bidirectional</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>CHEM-PRO-PIPE-001</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>CHEM-PRO-COLUMN-001</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>connects-to</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Piping</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>unidirectional</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>CHEM-FLD-FCV-002</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>CHEM-PRO-COLUMN-001</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>actuates</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>HART</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>unidirectional</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>CHEM-FLD-FCV-003</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>CHEM-PRO-HX-001</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>actuates</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>HART</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>unidirectional</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>CHEM-PRO-HX-001</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>CHEM-PRO-COLUMN-001</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>actuates</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Piping</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>unidirectional</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>CHEM-FLD-VALVE-001</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>CHEM-PRO-HX-001</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>actuates</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Modbus TCP</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>unidirectional</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>CHEM-FLD-PUMP-002</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>CHEM-PRO-TANK-001</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>actuates</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Modbus TCP</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>unidirectional</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>CHEM-SIS-SOV-001</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>CHEM-PRO-REACTOR-001</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>actuates</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>PROFIsafe</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>unidirectional</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>CHEM-SIS-SOV-002</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>CHEM-PRO-REACTOR-001</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>actuates</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>PROFIsafe</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>unidirectional</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>CHEM-CTL-DCS-003</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>CHEM-REM-RTU-001</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>controls</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>DNP3</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>bidirectional</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Leased line + VPN</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>CHEM-REM-SW-001</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>CHEM-REM-RTU-001</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>connects-to</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>DNP3</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>bidirectional</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>CHEM-REM-LT-001</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>CHEM-REM-RTU-001</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>monitors</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Modbus TCP</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>bidirectional</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>CHEM-REM-RTU-001</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>CHEM-REM-PUMP-001</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>actuates</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Modbus TCP</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>unidirectional</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>CHEM-REM-RTU-001</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>CHEM-REM-VALVE-001</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>actuates</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Modbus TCP</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>unidirectional</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>CHEM-REM-PUMP-001</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>CHEM-REM-TANK-001</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>actuates</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Modbus TCP</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>unidirectional</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>CHEM-REM-VALVE-001</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>CHEM-REM-TANK-001</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>actuates</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Modbus TCP</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>unidirectional</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
